--- a/results/ai_run/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/ai_run/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.1818</v>
+        <v>12.4545</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7944</v>
+        <v>6.3303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.7828</v>
+        <v>3.5009</v>
       </c>
       <c r="D25" t="n">
-        <v>4.5367</v>
+        <v>3.2405</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5172</v>
+        <v>0.9646</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M3" t="n">
         <v>754</v>
@@ -2738,7 +2738,7 @@
         <v>0.04515947</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.4748</v>
+        <v>4.1552</v>
       </c>
       <c r="Z3" t="n">
         <v>734</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>557</v>
@@ -2845,7 +2845,7 @@
         <v>0.04031197</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.7133</v>
+        <v>2.6524</v>
       </c>
       <c r="Z4" t="n">
         <v>505</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M5" t="n">
         <v>626</v>
@@ -2952,7 +2952,7 @@
         <v>0.0478417</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.699</v>
+        <v>5.9223</v>
       </c>
       <c r="Z5" t="n">
         <v>608</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>500</v>
@@ -3059,7 +3059,7 @@
         <v>0.03696034</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.2275</v>
+        <v>2.9585</v>
       </c>
       <c r="Z6" t="n">
         <v>403</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
         <v>479</v>
@@ -3166,7 +3166,7 @@
         <v>0.0441078</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.5367</v>
+        <v>3.2405</v>
       </c>
       <c r="Z7" t="n">
         <v>449</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
         <v>683</v>
@@ -3273,7 +3273,7 @@
         <v>0.05415771</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.2236</v>
+        <v>3.9177</v>
       </c>
       <c r="Z8" t="n">
         <v>670</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
         <v>497</v>
@@ -3380,7 +3380,7 @@
         <v>0.04353976</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.5678</v>
+        <v>2.6102</v>
       </c>
       <c r="Z9" t="n">
         <v>497</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
         <v>608</v>
@@ -3487,7 +3487,7 @@
         <v>0.03632146</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.0313</v>
+        <v>3.6591</v>
       </c>
       <c r="Z10" t="n">
         <v>578</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>566</v>
@@ -3594,7 +3594,7 @@
         <v>0.04998121</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.3656</v>
+        <v>3.0596</v>
       </c>
       <c r="Z11" t="n">
         <v>518</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
         <v>288</v>
@@ -3701,7 +3701,7 @@
         <v>0.03098468</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.4158</v>
+        <v>2.6567</v>
       </c>
       <c r="Z12" t="n">
         <v>211</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>139</v>
@@ -3808,7 +3808,7 @@
         <v>0.03196639</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.355</v>
+        <v>3.6775</v>
       </c>
       <c r="Z13" t="n">
         <v>124</v>
